--- a/docs/Phase0_02_画面設計書.xlsx
+++ b/docs/Phase0_02_画面設計書.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562294414948a666/ドキュメント/myWeb/RecipeSite/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76E3DC56-ABAB-4044-92D4-06F8B479C9B5}"/>
+  <xr:revisionPtr revIDLastSave="401" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BAEA308-931F-4B70-86F7-6DBB08D78E25}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="画面設計" sheetId="1" r:id="rId1"/>
     <sheet name="画面遷移設計" sheetId="3" r:id="rId2"/>
-    <sheet name="TOP画面" sheetId="2" r:id="rId3"/>
+    <sheet name="配色計画" sheetId="4" r:id="rId3"/>
+    <sheet name="TOP画面" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
   <si>
     <t>画面</t>
     <rPh sb="0" eb="2">
@@ -113,13 +114,299 @@
   <si>
     <t>Phase</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワイヤーフレーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>用途</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>色</t>
+    <rPh sb="0" eb="1">
+      <t>イロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メインカラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カード背景</t>
+    <rPh sb="3" eb="5">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#7c4a2d</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#fff4e6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#c6a477</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブカラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクセント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#fffcf7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字</t>
+    <rPh sb="0" eb="2">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>補助文字</t>
+    <rPh sb="0" eb="2">
+      <t>ホジョ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#f69552</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#4a2e1f</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#8f7a6a</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>色コード</t>
+    <rPh sb="0" eb="1">
+      <t>イロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完成イメージ</t>
+    <rPh sb="0" eb="2">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面構成</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンコウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トップバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LOGO、アプリ名を配置</t>
+    <rPh sb="8" eb="9">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピサムネイル部分</t>
+    <rPh sb="8" eb="10">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピサムネイルテーブル、もっと見るボタンを配置</t>
+    <rPh sb="16" eb="17">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検索部分</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>献立表示部分</t>
+    <rPh sb="0" eb="2">
+      <t>コンダテ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タグ一覧表示部分</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ヒョウジブブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル、検索バーを配置</t>
+    <rPh sb="5" eb="7">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル、朝の献立、昼の献立、夜の献立、献立表ページのリンクを配置</t>
+    <rPh sb="5" eb="6">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コンダテ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヒル</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コンダテ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヨル</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コンダテ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>コンダテヒョウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル、タグボタンを配置</t>
+    <rPh sb="11" eb="13">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パーツ名</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パーツ詳細</t>
+    <rPh sb="3" eb="5">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パーツNo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Header</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンポーネント名 (ファイル形式: .jsx)</t>
+    <rPh sb="7" eb="8">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ケイシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RecipeGrid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RecipeSearch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TodayMenu</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TagList</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘッダ用
+テキスト</t>
+    <rPh sb="3" eb="4">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#fff8f0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>URL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>色検索 - 原色大辞典</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,6 +419,14 @@
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -167,17 +462,35 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -335,15 +648,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>120650</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -358,8 +671,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3486150" y="1828800"/>
-          <a:ext cx="1892300" cy="657225"/>
+          <a:off x="3521075" y="2933700"/>
+          <a:ext cx="1812925" cy="654050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -398,16 +711,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>73025</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>120650</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>196850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>625475</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>168275</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -422,7 +735,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3486150" y="3044825"/>
+          <a:off x="6619875" y="2940050"/>
           <a:ext cx="1892300" cy="657225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -528,31 +841,33 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>196850</xdr:colOff>
+      <xdr:colOff>234950</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>174625</xdr:rowOff>
+      <xdr:rowOff>60325</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="10" name="コネクタ: カギ線 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F58413F-F29E-4E60-B12D-A4129CA1A993}"/>
+        <xdr:cNvPr id="11" name="コネクタ: カギ線 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1B83092-57E3-4615-96E2-50BEA6ED5843}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="3"/>
-          <a:endCxn id="5" idx="1"/>
+          <a:endCxn id="4" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2663825" y="2165350"/>
-          <a:ext cx="819150" cy="1209675"/>
+          <a:ext cx="857250" cy="1095375"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
         </a:prstGeom>
         <a:ln w="28575">
           <a:headEnd type="triangle"/>
@@ -578,35 +893,35 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>34925</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>98425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>196850</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>61914</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>69851</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="コネクタ: カギ線 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1B83092-57E3-4615-96E2-50BEA6ED5843}"/>
+        <xdr:cNvPr id="26" name="コネクタ: カギ線 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9272A90-BD43-4F83-815A-66ACB2818625}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="3"/>
-          <a:endCxn id="4" idx="1"/>
+          <a:stCxn id="5" idx="1"/>
+          <a:endCxn id="4" idx="3"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2663825" y="2155825"/>
-          <a:ext cx="819150" cy="9525"/>
+        <a:xfrm rot="10800000">
+          <a:off x="5334000" y="3262314"/>
+          <a:ext cx="1282700" cy="7937"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
@@ -637,35 +952,104 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>484188</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>488950</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>225425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="正方形/長方形 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27C98C32-18FF-44C7-A10D-3C1546E8B44B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3505200" y="1825625"/>
+          <a:ext cx="1854200" cy="660400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
+            <a:t>検索結果ページ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>34925</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>96838</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="23" name="コネクタ: カギ線 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EDB83AD-A05C-4873-8FEB-8EACC7FEEED4}"/>
+        <xdr:cNvPr id="25" name="コネクタ: カギ線 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7EDF0C0-A886-4366-8600-456D26D9A25E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="0"/>
-          <a:endCxn id="3" idx="2"/>
+          <a:stCxn id="24" idx="1"/>
+          <a:endCxn id="2" idx="3"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm rot="16200000" flipV="1">
-          <a:off x="4166394" y="1562894"/>
-          <a:ext cx="527050" cy="4762"/>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="2663825" y="2154238"/>
+          <a:ext cx="838200" cy="11112"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
@@ -697,42 +1081,39 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>482601</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:colOff>484188</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>495301</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>79375</xdr:rowOff>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>225425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="26" name="コネクタ: カギ線 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9272A90-BD43-4F83-815A-66ACB2818625}"/>
+        <xdr:cNvPr id="41" name="直線矢印コネクタ 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5656DF63-26F3-C582-E5FB-FA787D0CF0A7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="5" idx="0"/>
-          <a:endCxn id="4" idx="2"/>
+          <a:stCxn id="24" idx="0"/>
+          <a:endCxn id="3" idx="2"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm rot="5400000" flipH="1" flipV="1">
-          <a:off x="4151313" y="2763838"/>
-          <a:ext cx="561975" cy="12700"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 3073"/>
-          </a:avLst>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="4427538" y="1301750"/>
+          <a:ext cx="4762" cy="523875"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
         </a:prstGeom>
         <a:ln w="28575">
-          <a:headEnd type="triangle"/>
           <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
@@ -753,6 +1134,116 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>60325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="47" name="直線矢印コネクタ 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD922A7E-4FBC-DD0B-08AB-1DEF19AE084B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="3" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="5353050" y="974725"/>
+          <a:ext cx="904875" cy="835025"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>61913</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="50" name="直線矢印コネクタ 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4EF43A7-B4A8-4837-B765-94A99C7775BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="4" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5334000" y="1809750"/>
+          <a:ext cx="904875" cy="1452563"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -760,28 +1251,385 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>60871</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>98277</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>11758</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>218058</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>6351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2771775</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1579474</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E909FC3-672A-1FBF-EE3B-87C748E5A6D1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3560DA9-0648-1B10-4126-949D019FAC2C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1704975" y="463551"/>
+          <a:ext cx="2714625" cy="1573123"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2682875</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1564809</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5508AFF9-917E-8D5A-8CC7-89F1458E8089}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1743075" y="2124076"/>
+          <a:ext cx="2587625" cy="1498133"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>34925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2752725</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1277</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{654F52BA-77B8-A66E-7CC3-ADB7ED208BAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1692275" y="3692525"/>
+          <a:ext cx="2708275" cy="1566552"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>46460</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2714625</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1562203</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D26DF562-CB99-F237-B244-9A3743DDAEBE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6788150" y="503660"/>
+          <a:ext cx="2651125" cy="1515743"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2657475</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1524694</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{954C6BB0-8C35-4885-8E34-933923E52A7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6810375" y="2133600"/>
+          <a:ext cx="2571750" cy="1448494"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>82551</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2686050</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1557335</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD8B6F12-D621-C608-EFC1-EEDBCFE6CCAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6835776" y="3714751"/>
+          <a:ext cx="2603499" cy="1500184"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>53975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2689036</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1562204</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BD442CD-A687-CE42-0DD6-04CE3AFE99FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11715750" y="511175"/>
+          <a:ext cx="2593786" cy="1508229"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>133351</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>103548</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2698751</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1549501</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{278B8556-24C0-B129-9F2A-783F1EA573DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11830051" y="2160948"/>
+          <a:ext cx="2565400" cy="1445953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>403310</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>4666</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3721871</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>61953</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FB4D0E5-2251-3CEB-899A-92CFB76C3D16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -792,15 +1640,52 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="403310" y="468044"/>
+          <a:ext cx="9960318" cy="5154450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>654206</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1029" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FBB9DC9-F19E-24F2-E968-D221D91A9F10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="719390" y="321703"/>
-          <a:ext cx="7853109" cy="4811725"/>
+          <a:off x="1981200" y="7086600"/>
+          <a:ext cx="8991600" cy="6743700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -815,6 +1700,718 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>618816</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>217526</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3717074</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>84486</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE53AA20-E10E-3E5B-F168-8828C0C0911E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="618816" y="449843"/>
+          <a:ext cx="9742526" cy="563911"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>139391</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>23233</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>569177</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>220703</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79520748-194F-AEC7-8159-7FB26CCBB93B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="139391" y="720184"/>
+          <a:ext cx="429786" cy="429787"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>1</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635697</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>141481</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>433659</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>116158</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE33F4CF-1F2E-44E8-A700-C920FEF03C3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635697" y="1070749"/>
+          <a:ext cx="6442230" cy="4621019"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>130950</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>49640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>551211</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>8442</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{830C3325-B347-41D1-A78F-9BBA7DA2AEB4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="130950" y="1443542"/>
+          <a:ext cx="420261" cy="423437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>2</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>522172</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>139392</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3693842</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>144658</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CDA9556-057D-4485-9FC9-3D107DC22FF3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7166440" y="1068660"/>
+          <a:ext cx="3171670" cy="702218"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3841675</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>184460</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4254887</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>143262</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6662AECF-3AA7-41FF-99B4-E97C785372DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10485943" y="1113728"/>
+          <a:ext cx="413212" cy="423436"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>3</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>516828</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>184768</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3717074</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>8440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="正方形/長方形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFDC28F3-0102-4FB5-8131-A8710852082F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7161096" y="1810988"/>
+          <a:ext cx="3200246" cy="1914525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>524650</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>60170</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3732561</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>81310</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="正方形/長方形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28427398-F0DA-40D8-9058-616F5B48CA9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7168918" y="3777243"/>
+          <a:ext cx="3207911" cy="1879677"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3844154</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>182680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4263716</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>163708</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="正方形/長方形 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF1BAC28-23D5-4E54-AC7C-8FB532C4B84A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10488422" y="1808900"/>
+          <a:ext cx="419562" cy="445662"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>4</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3792424</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>101369</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4202461</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>85572</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="正方形/長方形 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC4D4ECC-9E79-49A1-90D3-AFC64E180411}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10436692" y="3818442"/>
+          <a:ext cx="410037" cy="448837"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>5</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>18382</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>144505</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>122022</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF7DD2FB-93F1-B022-A911-7E7586E16C9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12348175" y="481760"/>
+          <a:ext cx="10055654" cy="5200803"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1192,10 +2789,244 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21EA837-A9CC-4950-9ACF-C28B723F32F5}">
+  <dimension ref="B2:L8"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.4140625" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.4140625" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="38.4140625" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12">
+      <c r="B2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="126" customHeight="1">
+      <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="126" customHeight="1">
+      <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="126" customHeight="1">
+      <c r="B5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="C8" r:id="rId1" display="https://www.colordic.org/search" xr:uid="{8F244023-ADFB-4492-82D9-E50AFADC5A0A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F92740FC-038E-483C-98BF-ECF1C6C703DA}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="66.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7">
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30" s="1">
+        <v>2</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" s="1">
+        <v>3</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" s="1">
+        <v>4</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="1">
+        <v>5</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/docs/Phase0_02_画面設計書.xlsx
+++ b/docs/Phase0_02_画面設計書.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562294414948a666/ドキュメント/myWeb/RecipeSite/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="401" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BAEA308-931F-4B70-86F7-6DBB08D78E25}"/>
+  <xr:revisionPtr revIDLastSave="563" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F00216C-D5F1-4C5D-A6A5-515FA214F1BB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="画面設計" sheetId="1" r:id="rId1"/>
     <sheet name="画面遷移設計" sheetId="3" r:id="rId2"/>
     <sheet name="配色計画" sheetId="4" r:id="rId3"/>
-    <sheet name="TOP画面" sheetId="2" r:id="rId4"/>
+    <sheet name="TOPページ" sheetId="2" r:id="rId4"/>
+    <sheet name="レシピ閲覧ページ" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="88">
   <si>
     <t>画面</t>
     <rPh sb="0" eb="2">
@@ -62,10 +63,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>TOP画面</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>01</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -223,10 +220,6 @@
     <rPh sb="0" eb="4">
       <t>ガメンコウセイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>トップバー</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -400,6 +393,276 @@
   </si>
   <si>
     <t>色検索 - 原色大辞典</t>
+  </si>
+  <si>
+    <t>レシピカード部分</t>
+    <rPh sb="6" eb="8">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RecipeCard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピサムネイルを構成する1枚のカード</t>
+    <rPh sb="9" eb="11">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>料理の作り方や材料、画像などレシピ詳細が書かれたページ</t>
+    <rPh sb="0" eb="2">
+      <t>リョウリ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TOPページ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面構成</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンコウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘッダー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘッダー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TOPページの段階で作成済み</t>
+    <rPh sb="7" eb="9">
+      <t>ダンカイ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>サクセイズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>TOP画面遷移部分</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MovePageはあるページに遷移するコンポーネントとして作成（TOPページだけじゃないようにする）</t>
+    <rPh sb="15" eb="17">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピヘッダー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RecipeHeader</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピ名、調理時間を記載</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>チョウリジカン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピ説明部分</t>
+    <rPh sb="3" eb="5">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピ材料部分</t>
+    <rPh sb="3" eb="5">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作り方部分</t>
+    <rPh sb="0" eb="1">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピの作り方を載せる</t>
+    <rPh sb="4" eb="5">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピの材料、栄養情報ページへの遷移リンクを載せる</t>
+    <rPh sb="4" eb="6">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>エイヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピの説明を載せる</t>
+    <rPh sb="4" eb="6">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピ画像とレシピ説明、レシピ材料パーツを組み合わせて基本情報を載せる</t>
+    <rPh sb="3" eb="5">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>キホンジョウホウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピ概要部分</t>
+    <rPh sb="3" eb="5">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Header</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MovePage</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RecipeOverview</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RecipeDescription</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RecipeIngredients</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RecipeSteps</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -466,7 +729,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -484,10 +747,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -569,7 +834,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>画面</a:t>
+            <a:t>ページ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -633,7 +898,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>レシピ閲覧ページ</a:t>
+            <a:t>レシピ詳細ページ</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
         </a:p>
@@ -1615,9 +1880,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>3721871</xdr:colOff>
+      <xdr:colOff>3725046</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>61953</xdr:rowOff>
+      <xdr:rowOff>65128</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1664,8 +1929,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>654206</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>929</xdr:colOff>
       <xdr:row>59</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
@@ -1966,7 +2231,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
-            <a:t>2</a:t>
+            <a:t>3</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2069,6 +2334,947 @@
         <a:xfrm>
           <a:off x="10485943" y="1113728"/>
           <a:ext cx="413212" cy="423436"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>4</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>516828</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>184768</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3717074</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>8440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="正方形/長方形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFDC28F3-0102-4FB5-8131-A8710852082F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7161096" y="1810988"/>
+          <a:ext cx="3200246" cy="1914525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>524650</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>60170</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3732561</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>81310</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="正方形/長方形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28427398-F0DA-40D8-9058-616F5B48CA9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7168918" y="3777243"/>
+          <a:ext cx="3207911" cy="1879677"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3844154</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>182680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4263716</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>163708</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="正方形/長方形 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF1BAC28-23D5-4E54-AC7C-8FB532C4B84A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10488422" y="1808900"/>
+          <a:ext cx="419562" cy="445662"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>5</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3792424</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>101369</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4202461</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>85572</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="正方形/長方形 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC4D4ECC-9E79-49A1-90D3-AFC64E180411}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10436692" y="3818442"/>
+          <a:ext cx="410037" cy="448837"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>6</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>18382</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>141330</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>125197</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF7DD2FB-93F1-B022-A911-7E7586E16C9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12348175" y="481760"/>
+          <a:ext cx="10055654" cy="5200803"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>27555</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>77229</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>772297</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>167331</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3EC0A91-DDEC-4DDB-B4C6-C333DD8E09B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684008" y="3320878"/>
+          <a:ext cx="2031904" cy="1016858"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>143821</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>153204</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>564082</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>121531</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45856139-1B93-48F4-A29E-05199E8AA78D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="143821" y="3396853"/>
+          <a:ext cx="420261" cy="431705"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>2</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>25582</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>226572</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>894119</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>125866</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEE80467-C4C3-B504-4C4F-AA2D07A78CF5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="686500" y="693103"/>
+          <a:ext cx="6389150" cy="5727751"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180567</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>97877</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>604003</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>57310</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5B3A2B9-C794-489F-830F-7316A3F60A92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="180567" y="564408"/>
+          <a:ext cx="423436" cy="425963"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>1</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2102561</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>9082</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>7791</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5122E91C-C4E6-8C16-A949-F8DDCE3DD58B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8284092" y="708878"/>
+          <a:ext cx="6156990" cy="5598809"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>207476</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>942780</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>76058</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7101375-5598-4F54-BA46-106F2269ECCC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660920" y="674007"/>
+          <a:ext cx="6463391" cy="568378"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>272143</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>155508</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>716061</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>87474</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E06B1A0C-CBEF-4E6F-AFE7-57C5CD1BF8DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="933061" y="1321835"/>
+          <a:ext cx="443918" cy="165231"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>183937</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>159564</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>620073</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>122171</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5924831-BC71-46C1-977D-5FFBC51726DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="183937" y="1092625"/>
+          <a:ext cx="436136" cy="429138"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>2</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>648091</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>145791</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>962219</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>162055</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11964891-E217-4395-AAF2-434BAC5158A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="648091" y="1545383"/>
+          <a:ext cx="6495659" cy="249529"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>171043</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>182178</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>607179</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>144786</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0FBFD3F-D6CB-4D23-806C-C2E2A1CFC85C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="171043" y="1581770"/>
+          <a:ext cx="436136" cy="429138"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2106,23 +3312,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>516828</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>184768</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>3717074</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>8440</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161324</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>33213</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>597460</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>229085</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="正方形/長方形 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFDC28F3-0102-4FB5-8131-A8710852082F}"/>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9503D362-B176-4E8D-B62E-0135F8E38996}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2130,144 +3336,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7161096" y="1810988"/>
-          <a:ext cx="3200246" cy="1914525"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>524650</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>60170</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>3732561</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>81310</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="正方形/長方形 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28427398-F0DA-40D8-9058-616F5B48CA9A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7168918" y="3777243"/>
-          <a:ext cx="3207911" cy="1879677"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>3844154</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>182680</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>4263716</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>163708</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="正方形/長方形 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF1BAC28-23D5-4E54-AC7C-8FB532C4B84A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10488422" y="1808900"/>
-          <a:ext cx="419562" cy="445662"/>
+          <a:off x="161324" y="2599131"/>
+          <a:ext cx="436136" cy="429138"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2306,22 +3376,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>3792424</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>101369</xdr:rowOff>
+      <xdr:colOff>1116998</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>124057</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>4202461</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>85572</xdr:rowOff>
+      <xdr:colOff>1553134</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>86664</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="正方形/長方形 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC4D4ECC-9E79-49A1-90D3-AFC64E180411}"/>
+        <xdr:cNvPr id="14" name="正方形/長方形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1810B72-7023-44AA-8BEA-AF16FC1CEEAD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2329,8 +3399,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10436692" y="3818442"/>
-          <a:ext cx="410037" cy="448837"/>
+          <a:off x="7298529" y="1990179"/>
+          <a:ext cx="436136" cy="429138"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2366,56 +3436,462 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>-1</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>18382</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>144505</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>122022</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF7DD2FB-93F1-B022-A911-7E7586E16C9F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1113822</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>172653</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1549958</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>135260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F97DF61-E8E1-4D48-B276-8334E9E980C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12348175" y="481760"/>
-          <a:ext cx="10055654" cy="5200803"/>
+          <a:off x="7295353" y="3205102"/>
+          <a:ext cx="436136" cy="429138"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>6</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>193656</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>36582</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>626617</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>232455</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD8817CD-5667-4E50-858D-69F37359B5A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="193656" y="4701888"/>
+          <a:ext cx="432961" cy="429138"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+            <a:t>7</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>654635</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>217197</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>981658</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>181494</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="正方形/長方形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73207297-AB6F-406D-8175-A2BD6BBB4320}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="654635" y="1850054"/>
+          <a:ext cx="6508554" cy="2530216"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>531391</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>38878</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>894183</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>136071</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B99F21F2-0F0B-467E-8320-D2405AEBA219}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3913738" y="1905000"/>
+          <a:ext cx="3161976" cy="1030255"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>534565</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>178319</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>865025</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>116632</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="正方形/長方形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DDBC4D8-4215-4B8F-98A6-95D83208A9D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3916912" y="2977503"/>
+          <a:ext cx="3129644" cy="1337905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>657810</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>6546</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>971938</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>220371</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="正方形/長方形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADD56BF4-4CEA-4CA7-B5E6-D5EA54B5AD05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657810" y="4438587"/>
+          <a:ext cx="6495659" cy="1846682"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2021632</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171774</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1031051" cy="328423"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="テキスト ボックス 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4417CF8E-8AC1-68D9-5473-C708BA7ACBF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8203163" y="405039"/>
+          <a:ext cx="1031051" cy="328423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>完成イメージ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2694,7 +4170,7 @@
   <sheetData>
     <row r="2" spans="2:6">
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -2706,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="2:6">
@@ -2714,16 +4190,16 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="2:6">
@@ -2731,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>2</v>
@@ -2739,17 +4215,19 @@
       <c r="E4" s="1">
         <v>2</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="1">
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
@@ -2761,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>3</v>
@@ -2805,95 +4283,95 @@
   <sheetData>
     <row r="2" spans="2:12">
       <c r="B2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="L2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="126" customHeight="1">
       <c r="B3" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="126" customHeight="1">
       <c r="B4" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="126" customHeight="1">
       <c r="B5" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -2901,10 +4379,10 @@
     </row>
     <row r="8" spans="2:12">
       <c r="B8" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2920,7 +4398,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F92740FC-038E-483C-98BF-ECF1C6C703DA}">
-  <dimension ref="B2:G33"/>
+  <dimension ref="B2:G34"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
@@ -2931,29 +4409,29 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="2:5">
@@ -2961,13 +4439,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="2:5">
@@ -2975,13 +4453,13 @@
         <v>2</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="2:5">
@@ -2989,13 +4467,13 @@
         <v>3</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="2:5">
@@ -3003,13 +4481,13 @@
         <v>4</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="33" spans="2:5">
@@ -3017,13 +4495,167 @@
         <v>5</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>40</v>
       </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" s="1">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8DDE04C-EB0F-4C5C-8E87-03E2515B46B1}">
+  <dimension ref="B2:E37"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="91" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="D33" s="1" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>43</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Phase0_02_画面設計書.xlsx
+++ b/docs/Phase0_02_画面設計書.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562294414948a666/ドキュメント/myWeb/RecipeSite/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="563" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F00216C-D5F1-4C5D-A6A5-515FA214F1BB}"/>
+  <xr:revisionPtr revIDLastSave="702" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{807082E6-520A-4238-9581-00F19ED87203}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="画面設計" sheetId="1" r:id="rId1"/>
     <sheet name="画面遷移設計" sheetId="3" r:id="rId2"/>
     <sheet name="配色計画" sheetId="4" r:id="rId3"/>
-    <sheet name="TOPページ" sheetId="2" r:id="rId4"/>
-    <sheet name="レシピ閲覧ページ" sheetId="5" r:id="rId5"/>
+    <sheet name="配色計画_改" sheetId="6" r:id="rId4"/>
+    <sheet name="TOPページ" sheetId="2" r:id="rId5"/>
+    <sheet name="レシピ閲覧ページ" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="111">
   <si>
     <t>画面</t>
     <rPh sb="0" eb="2">
@@ -388,13 +389,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>URL</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>色検索 - 原色大辞典</t>
-  </si>
-  <si>
     <t>レシピカード部分</t>
     <rPh sb="6" eb="8">
       <t>ブブン</t>
@@ -662,6 +656,456 @@
   </si>
   <si>
     <t>RecipeSteps</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>命名</t>
+    <rPh sb="0" eb="2">
+      <t>メイメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景色</t>
+    <rPh sb="0" eb="3">
+      <t>ハイケイショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bg-brown</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bg-cream</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bg-ivory</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bg-orange</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキスト色</t>
+    <rPh sb="4" eb="5">
+      <t>ショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>text-dark-brown</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>text-gray-brown</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>text-warm-white</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>境界色</t>
+    <rPh sb="0" eb="3">
+      <t>キョウカイショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>border-tan</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>text-brown</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#654735</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>参考URL</t>
+    <rPh sb="0" eb="2">
+      <t>サンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.colordic.org/search</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">旧:メイン色(main)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ヘッダの背景色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ボタンの背景色
+などで使用</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ショク</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>ハイケイショク</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ハイケイショク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>旧:背景色(background)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ページ全体の背景で使用</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ショク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>旧：カード背景(card-background)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+レシピカードの背景
+説明欄の背景
+で使用</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>セツメイラン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>旧：アクセント(accent)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+手順番号
+ボタン背景
+などアクセントを入れる場面で使用</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>テジュンバンゴウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>バメン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>旧:補助文字(secondary-text)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+調理時間
+戻るページリンクテキスト
+などあまり目立たないようにする場面で使用</t>
+    </r>
+    <rPh sb="2" eb="6">
+      <t>ホジョモジ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>チョウリジカン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>メダ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>バメン</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">旧:文字(primary-text)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>見出しテキスト色
+として使用</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ミダ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ショク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>旧:ヘッダ用テキスト(header-text)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+背景が茶色系の見出し文字として使用</t>
+    </r>
+    <rPh sb="5" eb="6">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>チャイロケイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ミダ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新色
+説明文や普通のテキストとして使用</t>
+    <rPh sb="0" eb="2">
+      <t>シンショク</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>セツメイブン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>フツウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>旧:サブカラー(sub)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+境界線の色として使用</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キョウカイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シヨウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -669,7 +1113,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -690,6 +1134,29 @@
       <color theme="10"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -729,7 +1196,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -752,7 +1219,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1871,6 +2346,397 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>34925</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>111125</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2717800" cy="1573123"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA11D85A-40E3-42C2-BD19-2D4A9F7A44B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2130425" y="1025525"/>
+          <a:ext cx="2717800" cy="1573123"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2647950</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1650533</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2D4AA9E-E143-4070-88E5-1492CD27911B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2152650" y="2609850"/>
+          <a:ext cx="2590800" cy="1498133"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2708275" cy="1572902"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F468B7A5-B044-46F8-AD1A-8AEC9D94A1D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2120900" y="6121400"/>
+          <a:ext cx="2708275" cy="1572902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2682875</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1649093</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A271A66C-6A90-4717-86CC-AE906183E850}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2133600" y="6134100"/>
+          <a:ext cx="2644775" cy="1515743"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2660649</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1617659</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F54D1A19-8362-440B-9226-FE581ECE433B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9020175" y="809625"/>
+          <a:ext cx="2603499" cy="1493834"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2631886</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1673329</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A91E1CA-DDE4-4E85-9F7B-5BE1B997EDEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9001125" y="2619375"/>
+          <a:ext cx="2593786" cy="1511404"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2616200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1560253</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0960E20F-7BBF-4625-90C0-49A7B07E55BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9020175" y="4343400"/>
+          <a:ext cx="2562225" cy="1445953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>82550</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>2654300</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1610419</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E11F735-F873-4DED-889E-12DFCC86F938}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15808325" y="844550"/>
+          <a:ext cx="2571750" cy="1451669"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>57149</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2639246</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1619353</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F54E3D44-40E6-CDD9-1D2A-C88CC5207717}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10010774" y="6134100"/>
+          <a:ext cx="2578922" cy="1486003"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2815,7 +3681,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4193,7 +5059,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -4216,7 +5082,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="2:6">
@@ -4378,25 +5244,200 @@
       <c r="L5" s="1"/>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>54</v>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F56A723-3E56-45C7-995C-7641D056A5B6}">
+  <dimension ref="B2:O10"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.58203125" customWidth="1"/>
+    <col min="5" max="5" width="33.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.4140625" customWidth="1"/>
+    <col min="10" max="10" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.83203125" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:15">
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15">
+      <c r="B3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" ht="139.5" customHeight="1">
+      <c r="B4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="1"/>
+      <c r="O4" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="139.5" customHeight="1">
+      <c r="B5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" ht="139.5" customHeight="1">
+      <c r="B6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" ht="139.5" customHeight="1">
+      <c r="B7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15">
+      <c r="C10" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" display="https://www.colordic.org/search" xr:uid="{8F244023-ADFB-4492-82D9-E50AFADC5A0A}"/>
+    <hyperlink ref="D10" r:id="rId1" xr:uid="{E43C99E6-9CE2-4C42-8C57-527F70DB6242}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F92740FC-038E-483C-98BF-ECF1C6C703DA}">
   <dimension ref="B2:G34"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -4439,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>45</v>
@@ -4453,13 +5494,13 @@
         <v>2</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="31" spans="2:5">
@@ -4525,7 +5566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8DDE04C-EB0F-4C5C-8E87-03E2515B46B1}">
   <dimension ref="B2:E37"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -4543,7 +5584,7 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="2:5">
@@ -4562,30 +5603,30 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="10" t="s">
-        <v>65</v>
+      <c r="B32" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="2:5">
@@ -4593,69 +5634,69 @@
         <v>6</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="2:5">
       <c r="B35" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="10" t="s">
-        <v>67</v>
+      <c r="B36" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Phase0_02_画面設計書.xlsx
+++ b/docs/Phase0_02_画面設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562294414948a666/ドキュメント/myWeb/RecipeSite/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="702" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{807082E6-520A-4238-9581-00F19ED87203}"/>
+  <xr:revisionPtr revIDLastSave="705" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6173BCB2-D18D-426A-822E-15B1615FF0D7}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="画面設計" sheetId="1" r:id="rId1"/>
@@ -2515,22 +2515,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2660649</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1617659</xdr:rowOff>
+      <xdr:colOff>2631886</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1673329</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F54D1A19-8362-440B-9226-FE581ECE433B}"/>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A91E1CA-DDE4-4E85-9F7B-5BE1B997EDEB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2546,8 +2546,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9020175" y="809625"/>
-          <a:ext cx="2603499" cy="1493834"/>
+          <a:off x="9001125" y="2619375"/>
+          <a:ext cx="2593786" cy="1511404"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2559,22 +2559,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2631886</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>1673329</xdr:rowOff>
+      <xdr:colOff>2616200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1560253</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A91E1CA-DDE4-4E85-9F7B-5BE1B997EDEB}"/>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0960E20F-7BBF-4625-90C0-49A7B07E55BE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2590,8 +2590,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9001125" y="2619375"/>
-          <a:ext cx="2593786" cy="1511404"/>
+          <a:off x="9020175" y="4343400"/>
+          <a:ext cx="2562225" cy="1445953"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2602,23 +2602,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>82550</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2616200</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>1560253</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>2654300</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1610419</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0960E20F-7BBF-4625-90C0-49A7B07E55BE}"/>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E11F735-F873-4DED-889E-12DFCC86F938}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2634,8 +2634,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9020175" y="4343400"/>
-          <a:ext cx="2562225" cy="1445953"/>
+          <a:off x="15808325" y="844550"/>
+          <a:ext cx="2571750" cy="1451669"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2646,23 +2646,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>82550</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>57149</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>2654300</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1610419</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2639246</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1619353</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E11F735-F873-4DED-889E-12DFCC86F938}"/>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F54E3D44-40E6-CDD9-1D2A-C88CC5207717}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2678,8 +2678,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15808325" y="844550"/>
-          <a:ext cx="2571750" cy="1451669"/>
+          <a:off x="10010774" y="6134100"/>
+          <a:ext cx="2578922" cy="1486003"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2688,25 +2688,20 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2639246</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>1619353</xdr:rowOff>
-    </xdr:to>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>140686</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2584450" cy="1495937"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F54E3D44-40E6-CDD9-1D2A-C88CC5207717}"/>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE4CA93E-8DE2-42F0-8F0E-E77656AC2F31}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2715,15 +2710,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10010774" y="6134100"/>
-          <a:ext cx="2578922" cy="1486003"/>
+          <a:off x="9982200" y="826486"/>
+          <a:ext cx="2584450" cy="1495937"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2731,7 +2726,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/docs/Phase0_02_画面設計書.xlsx
+++ b/docs/Phase0_02_画面設計書.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562294414948a666/ドキュメント/myWeb/RecipeSite/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="705" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6173BCB2-D18D-426A-822E-15B1615FF0D7}"/>
+  <xr:revisionPtr revIDLastSave="706" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0222308B-5308-4740-9A2F-AC4683954A95}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="画面設計" sheetId="1" r:id="rId1"/>
     <sheet name="画面遷移設計" sheetId="3" r:id="rId2"/>
-    <sheet name="配色計画" sheetId="4" r:id="rId3"/>
+    <sheet name="配色計画" sheetId="4" state="hidden" r:id="rId3"/>
     <sheet name="配色計画_改" sheetId="6" r:id="rId4"/>
     <sheet name="TOPページ" sheetId="2" r:id="rId5"/>
     <sheet name="レシピ閲覧ページ" sheetId="5" r:id="rId6"/>
@@ -2396,7 +2396,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>2647950</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1650533</xdr:rowOff>
+      <xdr:rowOff>1647358</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2479,7 +2479,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>2682875</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>1649093</xdr:rowOff>
+      <xdr:rowOff>1645918</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2565,7 +2565,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2616200</xdr:colOff>
+      <xdr:colOff>2619375</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>1560253</xdr:rowOff>
     </xdr:to>
@@ -2609,9 +2609,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>2654300</xdr:colOff>
+      <xdr:colOff>2657475</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>1610419</xdr:rowOff>
+      <xdr:rowOff>1607244</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2653,7 +2653,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2639246</xdr:colOff>
+      <xdr:colOff>2636071</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>1619353</xdr:rowOff>
     </xdr:to>
